--- a/data/chinese/P2T3_Chapter9.xlsx
+++ b/data/chinese/P2T3_Chapter9.xlsx
@@ -8,14 +8,14 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D6485397-8CC4-0041-BA9E-F8E36B50369F}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8911EFB3-5438-5744-99AE-CB46A10B7CD5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="工作表1" sheetId="1" r:id="rId1"/>
-    <sheet name="工作表2" sheetId="3" r:id="rId2"/>
-    <sheet name="工作表3" sheetId="4" r:id="rId3"/>
+    <sheet name="必懂寫" sheetId="1" r:id="rId1"/>
+    <sheet name="只需記認" sheetId="3" r:id="rId2"/>
+    <sheet name="文章" sheetId="4" r:id="rId3"/>
   </sheets>
   <calcPr calcId="162913"/>
   <extLst>
@@ -1378,32 +1378,32 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
+        <v>69</v>
+      </c>
+      <c r="B1" t="s">
         <v>68</v>
-      </c>
-      <c r="B1" t="s">
-        <v>69</v>
       </c>
     </row>
     <row r="2" spans="1:2">
       <c r="A2" t="s">
+        <v>70</v>
+      </c>
+      <c r="B2" t="s">
         <v>64</v>
       </c>
-      <c r="B2" t="s">
-        <v>70</v>
-      </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="A3" t="s">
+      <c r="B3" t="s">
         <v>65</v>
       </c>
     </row>
     <row r="4" spans="1:2">
-      <c r="A4" t="s">
+      <c r="B4" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="5" spans="1:2">
-      <c r="A5" t="s">
+      <c r="B5" t="s">
         <v>67</v>
       </c>
     </row>

--- a/data/chinese/P2T3_Chapter9.xlsx
+++ b/data/chinese/P2T3_Chapter9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8911EFB3-5438-5744-99AE-CB46A10B7CD5}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118932B6-45F9-0144-8E1B-0A0EB62F43BF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="71">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
   <si>
     <t>生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -249,18 +249,6 @@
     <t>我等朋友等了很久。</t>
   </si>
   <si>
-    <t>朱雀橋邊野草花,</t>
-  </si>
-  <si>
-    <t>烏衣巷口夕陽斜。</t>
-  </si>
-  <si>
-    <t>舊時王 謝堂前燕,</t>
-  </si>
-  <si>
-    <t>飛入尋常百姓家。</t>
-  </si>
-  <si>
     <t>文章</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -270,6 +258,13 @@
   </si>
   <si>
     <t>烏衣巷 【唐】劉禹錫</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>朱雀橋邊野草花，
+烏衣巷口夕陽斜。
+舊時王 謝堂前燕，
+飛入尋常百姓家。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -357,7 +352,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -375,6 +370,9 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1373,39 +1371,34 @@
   <dimension ref="A1:B5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="2" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="21.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="19.1640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="B1" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="64">
       <c r="A2" t="s">
-        <v>70</v>
-      </c>
-      <c r="B2" t="s">
-        <v>64</v>
+        <v>66</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>67</v>
       </c>
     </row>
     <row r="3" spans="1:2">
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
+      <c r="B3" s="6"/>
     </row>
     <row r="4" spans="1:2">
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
+      <c r="B4" s="6"/>
     </row>
     <row r="5" spans="1:2">
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
+      <c r="B5" s="6"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>

--- a/data/chinese/P2T3_Chapter9.xlsx
+++ b/data/chinese/P2T3_Chapter9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{118932B6-45F9-0144-8E1B-0A0EB62F43BF}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9266D82-3E8E-DE4B-BAFE-3053B2ABA93D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -263,7 +263,7 @@
   <si>
     <t>朱雀橋邊野草花，
 烏衣巷口夕陽斜。
-舊時王 謝堂前燕，
+舊時王謝堂前燕，
 飛入尋常百姓家。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>

--- a/data/chinese/P2T3_Chapter9.xlsx
+++ b/data/chinese/P2T3_Chapter9.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C9266D82-3E8E-DE4B-BAFE-3053B2ABA93D}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED67B2F-A3AB-8240-A3BA-0C875C7133C1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必懂寫" sheetId="1" r:id="rId1"/>
@@ -1076,7 +1076,7 @@
         <v>37</v>
       </c>
       <c r="D4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="5"/>
     </row>
@@ -1106,7 +1106,7 @@
         <v>42</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5"/>
     </row>
@@ -1121,7 +1121,7 @@
         <v>45</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5"/>
     </row>
@@ -1136,7 +1136,7 @@
         <v>48</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E8" s="5"/>
     </row>
@@ -1151,7 +1151,7 @@
         <v>51</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="E9" s="5"/>
     </row>
@@ -1166,7 +1166,7 @@
         <v>54</v>
       </c>
       <c r="D10" s="3">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E10" s="5"/>
     </row>
@@ -1181,7 +1181,7 @@
         <v>57</v>
       </c>
       <c r="D11" s="3">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="E11" s="5"/>
     </row>
@@ -1196,7 +1196,7 @@
         <v>60</v>
       </c>
       <c r="D12" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E12" s="5"/>
     </row>
@@ -1211,7 +1211,7 @@
         <v>63</v>
       </c>
       <c r="D13" s="3">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="E13" s="5"/>
     </row>

--- a/data/chinese/P2T3_Chapter9.xlsx
+++ b/data/chinese/P2T3_Chapter9.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EED67B2F-A3AB-8240-A3BA-0C875C7133C1}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BAC236F-D966-544A-B749-27FB578C9DDC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -731,7 +731,7 @@
         <v>18</v>
       </c>
       <c r="D4" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
@@ -747,7 +747,7 @@
         <v>20</v>
       </c>
       <c r="D5" s="3">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
@@ -763,7 +763,7 @@
         <v>22</v>
       </c>
       <c r="D6" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
@@ -779,7 +779,7 @@
         <v>24</v>
       </c>
       <c r="D7" s="3">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
@@ -795,7 +795,7 @@
         <v>26</v>
       </c>
       <c r="D8" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
@@ -811,7 +811,7 @@
         <v>28</v>
       </c>
       <c r="D9" s="3">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>

--- a/data/chinese/P2T3_Chapter9.xlsx
+++ b/data/chinese/P2T3_Chapter9.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Moons/單詞複習網素材/Chinese/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/simonlam/My Files/Github/ChineseLearning/data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6BAC236F-D966-544A-B749-27FB578C9DDC}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3EFAFDAD-B81E-C346-8710-7C51B9CE6972}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="25600" yWindow="460" windowWidth="38400" windowHeight="21140" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="460" windowWidth="25600" windowHeight="15540" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="必懂寫" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="72" uniqueCount="68">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="69">
   <si>
     <t>生字</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -265,6 +265,14 @@
 烏衣巷口夕陽斜。
 舊時王謝堂前燕，
 飛入尋常百姓家。</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>【解釋】：朱雀橋的旁邊，長滿雜草、開著野花，冷冷清清。
+烏衣巷的巷口，夕陽斜斜地照過來，氣氛很蕭條。從前這裡是大官住的地方，非常熱鬧，現在變得荒涼。
+從前，燕子常在王、謝兩位大官的大宅屋檐下築巢。
+現在那些燕子，飛到普通老百姓的家裡去了。
+【簡單中心思想】：從前繁華富貴的地方，如今變得冷清。詩人感嘆繁榮不會永遠維持，世事會改變。</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -1368,36 +1376,43 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{45B55EBE-976A-904F-A78F-71BFD8B8303C}">
-  <dimension ref="A1:B5"/>
+  <dimension ref="A1:C5"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="21.33203125" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="19.1640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="34" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2">
+    <row r="1" spans="1:3">
       <c r="A1" t="s">
         <v>65</v>
       </c>
       <c r="B1" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" ht="64">
+      <c r="C1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" ht="208">
       <c r="A2" t="s">
         <v>66</v>
       </c>
       <c r="B2" s="6" t="s">
         <v>67</v>
       </c>
-    </row>
-    <row r="3" spans="1:2">
+      <c r="C2" s="6" t="s">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3">
       <c r="B3" s="6"/>
     </row>
-    <row r="4" spans="1:2">
+    <row r="4" spans="1:3">
       <c r="B4" s="6"/>
     </row>
-    <row r="5" spans="1:2">
+    <row r="5" spans="1:3">
       <c r="B5" s="6"/>
     </row>
   </sheetData>
